--- a/etf_holdings/2026-10-06_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:42</t>
+          <t>2026-10-06 01:23:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:42</t>
+          <t>2026-10-06 01:23:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:42</t>
+          <t>2026-10-06 01:23:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:42</t>
+          <t>2026-10-06 01:23:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:42</t>
+          <t>2026-10-06 01:23:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:42</t>
+          <t>2026-10-06 01:23:36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:42</t>
+          <t>2026-10-06 01:23:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:42</t>
+          <t>2026-10-06 01:23:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:42</t>
+          <t>2026-10-06 01:23:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:42</t>
+          <t>2026-10-06 01:23:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:42</t>
+          <t>2026-10-06 01:23:36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:42</t>
+          <t>2026-10-06 01:23:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:42</t>
+          <t>2026-10-06 01:23:36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:42</t>
+          <t>2026-10-06 01:23:36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:42</t>
+          <t>2026-10-06 01:23:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:43</t>
+          <t>2026-10-06 01:23:37</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:43</t>
+          <t>2026-10-06 01:23:37</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:43</t>
+          <t>2026-10-06 01:23:37</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:43</t>
+          <t>2026-10-06 01:23:37</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:43</t>
+          <t>2026-10-06 01:23:37</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:43</t>
+          <t>2026-10-06 01:23:37</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:43</t>
+          <t>2026-10-06 01:23:37</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:43</t>
+          <t>2026-10-06 01:23:37</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:43</t>
+          <t>2026-10-06 01:23:37</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:43</t>
+          <t>2026-10-06 01:23:37</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:43</t>
+          <t>2026-10-06 01:23:37</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:43</t>
+          <t>2026-10-06 01:23:37</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:43</t>
+          <t>2026-10-06 01:23:37</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:43</t>
+          <t>2026-10-06 01:23:37</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:43</t>
+          <t>2026-10-06 01:23:37</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:44</t>
+          <t>2026-10-06 01:23:38</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:44</t>
+          <t>2026-10-06 01:23:38</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:44</t>
+          <t>2026-10-06 01:23:38</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:44</t>
+          <t>2026-10-06 01:23:38</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:44</t>
+          <t>2026-10-06 01:23:38</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:44</t>
+          <t>2026-10-06 01:23:38</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:44</t>
+          <t>2026-10-06 01:23:38</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:44</t>
+          <t>2026-10-06 01:23:38</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:44</t>
+          <t>2026-10-06 01:23:38</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:44</t>
+          <t>2026-10-06 01:23:38</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:44</t>
+          <t>2026-10-06 01:23:38</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:44</t>
+          <t>2026-10-06 01:23:38</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:44</t>
+          <t>2026-10-06 01:23:38</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:44</t>
+          <t>2026-10-06 01:23:38</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:44</t>
+          <t>2026-10-06 01:23:38</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:46</t>
+          <t>2026-10-06 01:23:40</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:46</t>
+          <t>2026-10-06 01:23:40</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:46</t>
+          <t>2026-10-06 01:23:40</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:46</t>
+          <t>2026-10-06 01:23:40</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 01:14:46</t>
+          <t>2026-10-06 01:23:40</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:36</t>
+          <t>2026-10-06 02:27:13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:37</t>
+          <t>2026-10-06 02:27:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:38</t>
+          <t>2026-10-06 02:27:16</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:40</t>
+          <t>2026-10-06 02:27:17</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:40</t>
+          <t>2026-10-06 02:27:17</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:40</t>
+          <t>2026-10-06 02:27:17</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:40</t>
+          <t>2026-10-06 02:27:17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 01:23:40</t>
+          <t>2026-10-06 02:27:17</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:13</t>
+          <t>2026-10-06 23:18:53</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+3%2575</t>
+          <t>+0.39%2585</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+3%</t>
+          <t>+0.39%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2575</v>
+        <v>2585</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13.03%4,200,000</t>
+          <t>13.47%4,200,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.03%</t>
+          <t>13.47%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:13</t>
+          <t>2026-10-06 23:18:53</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+9.93%5700</t>
+          <t>+5.18%5995</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+9.93%</t>
+          <t>+5.18%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5700</v>
+        <v>5995</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8.69%1,350,000</t>
+          <t>10.04%1,350,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>8.69%</t>
+          <t>10.04%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:13</t>
+          <t>2026-10-06 23:18:53</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.76%530</t>
+          <t>-1.13%1310</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>-1.13%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>530</v>
+        <v>1310</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.49%13,000,000</t>
+          <t>8.58%5,280,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.49%</t>
+          <t>8.58%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>13000000</v>
+        <v>5280000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:13</t>
+          <t>2026-10-06 23:18:53</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+1.53%1325</t>
+          <t>-1.91%13100</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>-1.91%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1325</v>
+        <v>13100</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8.42%5,200,000</t>
+          <t>7.64%470,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>8.42%</t>
+          <t>7.64%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5200000</v>
+        <v>470000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:13</t>
+          <t>2026-10-06 23:18:53</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+9.96%13355</t>
+          <t>-0.94%525</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-0.94%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>13355</v>
+        <v>525</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.24%480,000</t>
+          <t>7.62%11,700,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>7.24%</t>
+          <t>7.62%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>480000</v>
+        <v>11700000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.68%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:13</t>
+          <t>2026-10-06 23:18:53</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,33 +814,33 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+4.34%5165</t>
+          <t>-4.74%4920</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+4.34%</t>
+          <t>-4.74%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5165</v>
+        <v>4920</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.94%1,130,000</t>
+          <t>6.72%1,100,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.94%</t>
+          <t>6.72%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1130000</v>
+        <v>1100000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:13</t>
+          <t>2026-10-06 23:18:53</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+2.4%1495</t>
+          <t>+0.67%1505</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1495</v>
+        <v>1505</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6.16%3,400,000</t>
+          <t>6.35%3,400,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:13</t>
+          <t>2026-10-06 23:18:53</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,33 +936,33 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+4.29%1095</t>
+          <t>-2.28%1070</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+4.29%</t>
+          <t>-2.28%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1095</v>
+        <v>1070</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.86%4,500,000</t>
+          <t>6.13%4,620,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.86%</t>
+          <t>6.13%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4500000</v>
+        <v>4620000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:13</t>
+          <t>2026-10-06 23:18:53</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+4.22%3585</t>
+          <t>+2.79%3685</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+4.22%</t>
+          <t>+2.79%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3585</v>
+        <v>3685</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.34%1,250,000</t>
+          <t>5.72%1,250,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.34%</t>
+          <t>5.72%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:13</t>
+          <t>2026-10-06 23:18:53</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,33 +1058,33 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0%626</t>
+          <t>-0.16%625</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.66%6,000,000</t>
+          <t>4.50%5,800,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.66%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6000000</v>
+        <v>5800000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:13</t>
+          <t>2026-10-06 23:18:53</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+3.61%19520</t>
+          <t>-2.74%18985</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+3.61%</t>
+          <t>-2.74%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>19520</v>
+        <v>18985</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.29%140,500</t>
+          <t>3.31%140,500</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.31%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:13</t>
+          <t>2026-10-06 23:18:53</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+3.12%2150</t>
+          <t>+6.51%2290</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+3.12%</t>
+          <t>+6.51%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2150</v>
+        <v>2290</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.98%1,150,020</t>
+          <t>3.27%1,150,020</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>3.27%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:13</t>
+          <t>2026-10-06 23:18:53</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+2.56%3000</t>
+          <t>+2.45%293</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>+2.45%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3000</v>
+        <v>293</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.90%800,000</t>
+          <t>3.09%8,500,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>3.09%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>800000</v>
+        <v>8500000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:13</t>
+          <t>2026-10-06 23:18:53</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.16%817</t>
+          <t>-2.67%2920</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>-2.67%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>817</v>
+        <v>2920</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.80%2,700,000</t>
+          <t>2.90%800,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.90%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>2700000</v>
+        <v>800000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:13</t>
+          <t>2026-10-06 23:18:53</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+10%286</t>
+          <t>-2.57%796</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-2.57%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>286</v>
+        <v>796</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.58%8,000,000</t>
+          <t>2.57%2,600,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.58%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>8000000</v>
+        <v>2600000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:15</t>
+          <t>2026-10-06 23:18:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+5.96%7205</t>
+          <t>-1.73%7080</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+5.96%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>7205</v>
+        <v>7080</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.45%290,000</t>
+          <t>2.55%290,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.55%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:15</t>
+          <t>2026-10-06 23:18:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-5.57%152.5</t>
+          <t>+2.24%2050</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.57%</t>
+          <t>+2.24%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>152.5</v>
+        <v>2050</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.08%10,400,000</t>
+          <t>1.65%650,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.08%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>10400000</v>
+        <v>650000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:15</t>
+          <t>2026-10-06 23:18:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+6.37%2005</t>
+          <t>+0.27%744</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+6.37%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2005</v>
+        <v>744</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.04%871,000</t>
+          <t>1.57%1,700,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>871000</v>
+        <v>1700000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:15</t>
+          <t>2026-10-06 23:18:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>6505台塑化</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+4.07%742</t>
+          <t>+2.94%101.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+4.07%</t>
+          <t>+2.94%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>742</v>
+        <v>101.5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.50%1,700,000</t>
+          <t>1.07%8,500,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.07%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1700000</v>
+        <v>8500000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:15</t>
+          <t>2026-10-06 23:18:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6505台塑化</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-1.4%98.6</t>
+          <t>+1.86%6855</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+1.86%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>98.59999999999999</v>
+        <v>6855</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.05%8,500,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>8500000</v>
+        <v>1000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:15</t>
+          <t>2026-10-06 23:18:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+5.6%2075</t>
+          <t>+1.55%5905</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+5.6%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2075</v>
+        <v>5905</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.49%200,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>200000</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:15</t>
+          <t>2026-10-06 23:18:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,21 +1785,21 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+7%6730</t>
+          <t>+2.72%5670</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>+2.72%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>6730</v>
+        <v>5670</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:15</t>
+          <t>2026-10-06 23:18:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,25 +1846,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>2382廣達</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+4.21%5815</t>
+          <t>+0.76%333.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+4.21%</t>
+          <t>+0.76%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5815</v>
+        <v>333.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:15</t>
+          <t>2026-10-06 23:18:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,21 +1907,21 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+3.95%5520</t>
+          <t>+1.08%2350</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+3.95%</t>
+          <t>+1.08%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>5520</v>
+        <v>2350</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:15</t>
+          <t>2026-10-06 23:18:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,21 +1968,21 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2382廣達</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.3%331</t>
+          <t>+0.79%256</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>+0.79%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>331</v>
+        <v>256</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:15</t>
+          <t>2026-10-06 23:18:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-2.17%2485</t>
+          <t>-6.44%2325</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-2.17%</t>
+          <t>-6.44%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>2485</v>
+        <v>2325</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:15</t>
+          <t>2026-10-06 23:18:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,21 +2090,21 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>2603長榮</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+1.2%254</t>
+          <t>+0.85%236.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>254</v>
+        <v>236.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:15</t>
+          <t>2026-10-06 23:18:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,21 +2151,21 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+6.16%2325</t>
+          <t>-1.2%2050</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2325</v>
+        <v>2050</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:15</t>
+          <t>2026-10-06 23:18:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2603長榮</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.29%234.5</t>
+          <t>-0.48%2090</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.29%</t>
+          <t>-0.48%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>234.5</v>
+        <v>2090</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:15</t>
+          <t>2026-10-06 23:18:55</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.24%2100</t>
+          <t>0%189.5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2100</v>
+        <v>189.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:16</t>
+          <t>2026-10-06 23:18:56</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+9.88%1780</t>
+          <t>-1.4%1755</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+9.88%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1780</v>
+        <v>1755</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:16</t>
+          <t>2026-10-06 23:18:56</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,21 +2395,21 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.61%189.5</t>
+          <t>+3.8%191</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.61%</t>
+          <t>+3.8%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>189.5</v>
+        <v>191</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:16</t>
+          <t>2026-10-06 23:18:56</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,21 +2456,21 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>2881富邦金</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.6%184</t>
+          <t>+1.64%154.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>184</v>
+        <v>154.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:16</t>
+          <t>2026-10-06 23:18:56</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,21 +2517,21 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2881富邦金</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1%152</t>
+          <t>-3.28%147.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>-3.28%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>152</v>
+        <v>147.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:16</t>
+          <t>2026-10-06 23:18:56</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2882國泰金</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0%111.5</t>
+          <t>+0.5%1000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.5%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>111.5</v>
+        <v>1000</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:16</t>
+          <t>2026-10-06 23:18:56</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>2882國泰金</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+3.43%995</t>
+          <t>+0.45%112</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+3.43%</t>
+          <t>+0.45%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>995</v>
+        <v>112</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:16</t>
+          <t>2026-10-06 23:18:56</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.13%755</t>
+          <t>0%755</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:16</t>
+          <t>2026-10-06 23:18:56</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+2.1%68.2</t>
+          <t>+1.61%69.3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>+1.61%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>68.2</v>
+        <v>69.3</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:16</t>
+          <t>2026-10-06 23:18:56</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,25 +2822,25 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2891中信金</t>
+          <t>3044健鼎</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.15%67.4</t>
+          <t>+3.95%579</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>+3.95%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>67.40000000000001</v>
+        <v>579</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:16</t>
+          <t>2026-10-06 23:18:56</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,25 +2883,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3044健鼎</t>
+          <t>2891中信金</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+2.77%557</t>
+          <t>+1.48%68.4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+2.77%</t>
+          <t>+1.48%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>557</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:16</t>
+          <t>2026-10-06 23:18:56</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,25 +2944,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>2890永豐金</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.51%294</t>
+          <t>+3.06%45.4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>+3.06%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>294</v>
+        <v>45.4</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,450</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -2971,11 +2971,11 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1450</v>
+        <v>9000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:16</t>
+          <t>2026-10-06 23:18:56</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,21 +3005,21 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2884玉山金</t>
+          <t>2886兆豐金</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.21%44.8</t>
+          <t>+1.54%49.3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+1.54%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>44.8</v>
+        <v>49.3</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:16</t>
+          <t>2026-10-06 23:18:56</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2886兆豐金</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.61%48.55</t>
+          <t>+1.36%298</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>48.55</v>
+        <v>298</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,450</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>9000</v>
+        <v>1450</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:16</t>
+          <t>2026-10-06 23:18:56</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2880華南金</t>
+          <t>2884玉山金</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.56%44.6</t>
+          <t>+1.45%45.45</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.56%</t>
+          <t>+1.45%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>44.6</v>
+        <v>45.45</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,090</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,11 +3154,11 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>9090</v>
+        <v>9000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:16</t>
+          <t>2026-10-06 23:18:56</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,34 +3188,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2883凱基金</t>
+          <t>2880華南金</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.13%37.3</t>
+          <t>+1.91%45.45</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>37.3</v>
+        <v>45.45</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0%9,000</t>
+          <t>&lt;0.01%9,090</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>&lt;0.01%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>9000</v>
+        <v>9090</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:17</t>
+          <t>2026-10-06 23:18:57</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,21 +3249,21 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2887台新新光金</t>
+          <t>2883凱基金</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+0.74%40.85</t>
+          <t>+0.94%37.65</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+0.74%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>40.85</v>
+        <v>37.65</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:17</t>
+          <t>2026-10-06 23:18:57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,21 +3310,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2890永豐金</t>
+          <t>2887台新新光金</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0%44.05</t>
+          <t>+1.47%41.45</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>44.05</v>
+        <v>41.45</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:17</t>
+          <t>2026-10-06 23:18:57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+9.96%248.5</t>
+          <t>+1.41%252</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>248.5</v>
+        <v>252</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:17</t>
+          <t>2026-10-06 23:18:57</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0%213.5</t>
+          <t>+0.7%215</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.7%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>213.5</v>
+        <v>215</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 02:27:17</t>
+          <t>2026-10-06 23:18:57</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.34%145.5</t>
+          <t>0%145.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H51" t="n">

--- a/etf_holdings/2026-10-06_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:53</t>
+          <t>2026-10-06 23:27:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:53</t>
+          <t>2026-10-06 23:27:24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:53</t>
+          <t>2026-10-06 23:27:24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:53</t>
+          <t>2026-10-06 23:27:24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:53</t>
+          <t>2026-10-06 23:27:24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:53</t>
+          <t>2026-10-06 23:27:24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:53</t>
+          <t>2026-10-06 23:27:24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:53</t>
+          <t>2026-10-06 23:27:24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:53</t>
+          <t>2026-10-06 23:27:24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:53</t>
+          <t>2026-10-06 23:27:24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:53</t>
+          <t>2026-10-06 23:27:24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:53</t>
+          <t>2026-10-06 23:27:24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:53</t>
+          <t>2026-10-06 23:27:24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:53</t>
+          <t>2026-10-06 23:27:24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:53</t>
+          <t>2026-10-06 23:27:24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:55</t>
+          <t>2026-10-06 23:27:25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:55</t>
+          <t>2026-10-06 23:27:25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:55</t>
+          <t>2026-10-06 23:27:25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:55</t>
+          <t>2026-10-06 23:27:25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:55</t>
+          <t>2026-10-06 23:27:25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:55</t>
+          <t>2026-10-06 23:27:25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:55</t>
+          <t>2026-10-06 23:27:25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:55</t>
+          <t>2026-10-06 23:27:25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:55</t>
+          <t>2026-10-06 23:27:25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:55</t>
+          <t>2026-10-06 23:27:25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:55</t>
+          <t>2026-10-06 23:27:25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:55</t>
+          <t>2026-10-06 23:27:25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:55</t>
+          <t>2026-10-06 23:27:25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:55</t>
+          <t>2026-10-06 23:27:25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:55</t>
+          <t>2026-10-06 23:27:25</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:56</t>
+          <t>2026-10-06 23:27:26</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:56</t>
+          <t>2026-10-06 23:27:26</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:56</t>
+          <t>2026-10-06 23:27:26</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:56</t>
+          <t>2026-10-06 23:27:26</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:56</t>
+          <t>2026-10-06 23:27:26</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:56</t>
+          <t>2026-10-06 23:27:26</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:56</t>
+          <t>2026-10-06 23:27:26</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:56</t>
+          <t>2026-10-06 23:27:26</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:56</t>
+          <t>2026-10-06 23:27:26</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:56</t>
+          <t>2026-10-06 23:27:26</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:56</t>
+          <t>2026-10-06 23:27:26</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:56</t>
+          <t>2026-10-06 23:27:26</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:56</t>
+          <t>2026-10-06 23:27:26</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:56</t>
+          <t>2026-10-06 23:27:26</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:56</t>
+          <t>2026-10-06 23:27:26</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:57</t>
+          <t>2026-10-06 23:27:28</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:57</t>
+          <t>2026-10-06 23:27:28</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:57</t>
+          <t>2026-10-06 23:27:28</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:57</t>
+          <t>2026-10-06 23:27:28</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 23:18:57</t>
+          <t>2026-10-06 23:27:28</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-06_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-06_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:24</t>
+          <t>2026-10-06 23:57:56</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:25</t>
+          <t>2026-10-06 23:57:57</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:26</t>
+          <t>2026-10-06 23:57:58</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:28</t>
+          <t>2026-10-06 23:58:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:28</t>
+          <t>2026-10-06 23:58:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:28</t>
+          <t>2026-10-06 23:58:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:28</t>
+          <t>2026-10-06 23:58:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-06 23:27:28</t>
+          <t>2026-10-06 23:58:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
